--- a/examples/sample_tests.xlsx
+++ b/examples/sample_tests.xlsx
@@ -425,144 +425,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>order</t>
+          <t>Suite Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>Suite Description</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>test_name</t>
+          <t>Prompt</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>prompt</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>expected_result</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>validation_type</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>temperature</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>max_tokens</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="b">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Smoke Suite</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Basic health-check prompts.</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Greeting test</t>
+          <t>Say hello in one sentence.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>Say hello in one sentence.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Hello</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>contains</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I2" t="n">
-        <v>64</v>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>Basic greeting</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="b">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Smoke Suite</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Basic health-check prompts.</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Summarization test</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
           <t>Summarize: PromptOps manages AI endpoints and tests.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>PromptOps</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>contains</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>summary</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>128</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PT-BR Suite</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Portuguese prompts for quick checks.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Explique em duas frases o que e PromptOps.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Idioma portugues</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
